--- a/artfynd/A 59940-2021 artfynd.xlsx
+++ b/artfynd/A 59940-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59940-2021 artfynd.xlsx
+++ b/artfynd/A 59940-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97261107</v>
+        <v>97261004</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596081.4081983962</v>
+        <v>596134</v>
       </c>
       <c r="R2" t="n">
-        <v>6431263.248657064</v>
+        <v>6431254</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +755,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,40 +785,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97260988</v>
+        <v>97261107</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -848,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596115.1720999577</v>
+        <v>596081</v>
       </c>
       <c r="R3" t="n">
-        <v>6431206.289950804</v>
+        <v>6431263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,19 +865,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,44 +895,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97261004</v>
+        <v>97260988</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596134.1907212971</v>
+        <v>596115</v>
       </c>
       <c r="R4" t="n">
-        <v>6431254.449685493</v>
+        <v>6431206</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,19 +971,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,12 +1004,7 @@
         <v>97261133</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596072.7305135987</v>
+        <v>596073</v>
       </c>
       <c r="R5" t="n">
-        <v>6431248.729343398</v>
+        <v>6431249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,19 +1081,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
